--- a/Field-trails/2025-10-14-inital-lab-acidification/2025-11-11-Titration-cattle-3rd.xlsx
+++ b/Field-trails/2025-10-14-inital-lab-acidification/2025-11-11-Titration-cattle-3rd.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-acidification-test-before-lab-field-trails\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Field-trails\2025-10-14-inital-lab-acidification\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3440259-3B15-4AF5-9BC4-B1399921396E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{370B1486-55E8-4919-B07A-20702458AF4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw data" sheetId="1" r:id="rId1"/>
@@ -212,13 +212,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6728,7 +6729,7 @@
       <c r="A7" s="2">
         <v>0.5</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="6">
         <f>'Data overview'!A7/Constants!$B$1*10^-3</f>
         <v>2.5</v>
       </c>
@@ -6736,7 +6737,7 @@
         <f>(Constants!B$2*'Data overview'!A7*10^-3)/Constants!$B$1</f>
         <v>4.7092499999999999</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="6">
         <f>'Raw data'!AE8</f>
         <v>6.59</v>
       </c>
